--- a/exit_interview_templates/049_counselor_exit_offboarding_form--exit_interview_templates.xlsx
+++ b/exit_interview_templates/049_counselor_exit_offboarding_form--exit_interview_templates.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -510,12 +510,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>exit_offboarding_form_page_1</t>
+          <t>counselor_info</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>First Day</t>
+          <t>Counselor Information</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -528,17 +528,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>exit_offboarding_form_page_2</t>
+          <t>last_day_info</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Last Day</t>
+          <t>Last Day Information</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -551,23 +551,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>exit_offboarding_form_page_3</t>
+          <t>reason_for_leaving</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Reason for Leaving</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>exit_offboarding_form_page_4</t>
+          <t>comments_last_day</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Comments on Last Day</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -597,481 +597,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>exit_offboarding_form_page_5</t>
+          <t>comments_exit_process</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Comments on Exit Process</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>exit_offboarding_form_page_6</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>exit_offboarding_form_page_7</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Exit Date</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>exit_offboarding_form_page_8</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Last Day Comments</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>exit_offboarding_form_page_9</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Last Day Time</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>exit_offboarding_form_page_10</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Exit Date Comments</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>exit_offboarding_form_page_11</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>exit_offboarding_form_page_12</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>exit_offboarding_form_page_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>exit_offboarding_form_page_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>exit_offboarding_form_page_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>exit_offboarding_form_page_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>exit_offboarding_form_page_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>exit_offboarding_form_page_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>exit_offboarding_form_page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>exit_offboarding_form_page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>exit_offboarding_form_page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>exit_offboarding_form_page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>exit_offboarding_form_page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>exit_offboarding_form_page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>exit_offboarding_form_page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
